--- a/tools/sim/HearthCraft_Encounter_Builder.xlsx
+++ b/tools/sim/HearthCraft_Encounter_Builder.xlsx
@@ -31,6 +31,7 @@
     <sheet name="L22 · Barrow-wight Lord" sheetId="16" r:id="rId16"/>
     <sheet name="L22 · Barrow-downs" sheetId="17" r:id="rId17"/>
     <sheet name="L40 · Ringwraith" sheetId="18" r:id="rId18"/>
+    <sheet name="Design Notes" sheetId="19" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -5534,6 +5535,730 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>HearthCraft -- Encounter Design Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Philosophy, food ladders, and tuning rationale for every encounter in the difficulty ramp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Keep this sheet updated whenever an encounter is tuned or a new one is added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DESIGN PHILOSOPHY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Each rung of the difficulty ladder adds exactly one new question the fight asks. Early content (Rungs 0-2) has no Dread or Shadow by construction -- those are the last two hazards and cannot appear until the player has mastered the fundamentals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Food ladder rule: each encounter should have a win window spanning ~3-4 consecutive recipe levels. Lv1 of the tier = occasional win (~20-30%). Mid-tier = squeaky zone (55-70%). Tier ceiling = comfortable (95%+). Next tier entry = near-pristine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Spike variance: interval is randomised +/-50% around mean, damage +/-30% around base. Breaks the binary win/loss cliff that fixed spikes produce. Creates genuine run-to-run variance and near-miss stories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HP/s curve: convex within each tier (power=1.8). Small gains at tier entry, biggest reward approaching tier ceiling. Pulls players toward the next tier rather than farming the current one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PhysMit: do not add armor until Rung 1 (mailed orcs, stone-trolls). Early encounters are pure sustain tests -- armor would confuse the lesson before penetration mechanics are introduced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dread: do not add until Rung 5 (barrow-wights, the Dead). Dread suppresses DPS -- the player must already understand the win axis before it is taken away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shadow: do not add until Rung 6 (great spiders, Balrog, the Nine). Shadow drains Will+Fate over time -- the deepest mechanic, reserved for the deepest content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DIFFICULTY RAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rung</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>New question</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Teacher foes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Provisioning answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Survive + win at all?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Neekerbreekers, wolves, lone goblins</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bree-land, Midgewater, Chetwood</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HP/s food + damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pierce armor?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mailed orcs, stone-trolls</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Trollshaws, Goblin-town</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Agi/Mig food (penetration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Weather the dice?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Warg packs, barghests</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Misty Mountain passes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Feed fragile members; respect Keeper 5-rescue cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Have the region antidote?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Huorns, midge-marsh, cold passes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Old Forest, Midgewater, Caradhras</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>One hazard food (Alert / Hale / Warmth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Endure when you cannot win?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Old Man Willow, blizzard</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Old Forest, high passes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>All-sustain; survival mindset</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fight while afraid?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Barrow-wights, the Dead</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Barrow-downs, Dead Marshes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Hope food + Captain Will</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fight while the light fails?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Great spiders, Balrog, the Nine</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mirkwood, Moria, Morgul-vale</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Radiance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All at once.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sieges, combined raids</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fornost, the Black Gate</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Multi-stage prep, the full toolkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ENCOUNTER NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>encounter</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>recLevel</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>rung</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>food ladder (win rates by recipe level)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>phys mit</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>hazards</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>tuning notes and validation status</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Neekerbreekers at the Marsh's Edge</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lv1=25% / Lv2=66% / Lv3=98% / Lv4=100%  -- confirmed 5000 runs</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>None -- no armor in Rung 0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>None -- pure drain+spike sustain test</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>drain=12 spike=75 iv=13 (mean, +/-50% jitter) resolve=50000 duration=1500. Drain-dominant tutorial fight. Unwinnable with no food (wipe ~1min). Squeaky with Lv1-2. Clean from Lv3. The lesson is: go cook. VALIDATED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Wolves in the Chetwood</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TBD -- tune after Neekers ladder is locked. Target: Lv4 (Neekers ceiling) = squeaky entry, Lv6-7 = comfortable.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>None -- second pure sustain test, raises bar from Neekers</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Adds second question: sustain AND whether Warden can hold the line for the Keeper. Food bar should roughly double vs Neekers. Numbers not yet validated -- run sim sweep before locking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>(add rows here as encounters are tuned and validated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HP/s TIER TABLE  (convex curve, power=1.8 within each tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cook Lv</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HP/s range</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Per-level values</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hearthkeeper</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5 - 10</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Lv1=5.0  Lv2=5.7  Lv3=7.4  Lv4=10.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Initiate</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>10 - 18</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Lv5=10.0  Lv6=10.7  Lv7=12.3  Lv8=14.8  Lv9=18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Apprentice</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10-15</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>18 - 30</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Lv10=18.0  Lv11=22.2  Lv12=24.6  Lv13=26.6  Lv14=28.4  Lv15=30.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Journeyman</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16-22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>30 - 44</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Lv16=30.0  Lv17=34.4  Lv18=36.9  Lv19=38.9  Lv20=40.8  Lv21=42.4  Lv22=44.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Adept</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>23-30</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>44 - 62</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Lv23=44.0  Lv24=49.1  Lv25=52.0  Lv26=54.4  Lv27=56.5  Lv28=58.5  Lv29=60.3  Lv30=62.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>31-40</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>62 - 86</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Lv31=62.0  Lv32=67.8  Lv33=71.0  Lv34=73.8  Lv35=76.2  Lv36=78.4  Lv37=80.4  Lv38=82.4  Lv39=84.2  Lv40=86.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Grandmaster</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>41-50</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>86 - 110</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Lv41=86.0  Lv42=91.8  Lv43=95.0  Lv44=97.8  Lv45=100.2  Lv46=102.4  Lv47=104.4  Lv48=106.4  Lv49=108.2  Lv50=110.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AFTER-ACTION REPORT DESIGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>The after-action report does the emotional work that the binary win/loss outcome cannot. A player who loses with the enemy at 8% resolve should see that number -- it turns an opaque failure into a near-miss story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Well-provisioned: low variance, consistent wins, clean aftermath. Preparation is rewarded reliably.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Squeaky zone: high variance, sometimes win, sometimes lose. Aftermath always explains why -- enemy resolve remaining, wounds, rescues spent, Inspirations that fired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Underprepared: consistent fast wipe. The lesson is clear and fast: go level up your cooking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Key stats to surface: enemy resolve remaining at defeat (%), fight duration, wounds per member, rescues used / Warden guards spent, Inspirations fired, one-line verdict.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>

--- a/tools/sim/HearthCraft_Encounter_Builder.xlsx
+++ b/tools/sim/HearthCraft_Encounter_Builder.xlsx
@@ -1317,12 +1317,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF4A2F1A"/>
   </sheetPr>
   <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1339,22 +1339,22 @@
     <col min="17" max="17" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ns3:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ns3:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ns3:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ns3:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>3</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ns3:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>20</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ns3:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>24</v>
       </c>
@@ -1477,16 +1477,16 @@
         <v>1500</v>
       </c>
       <c r="F7" s="19">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="G7" s="19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H7" s="19">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I7" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J7" s="19">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ns3:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>26</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ns3:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>29</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ns3:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>31</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ns3:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>33</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ns3:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>35</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ns3:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>38</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ns3:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>40</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ns3:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>42</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ns3:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>44</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ns3:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>46</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ns3:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>48</v>
       </c>

--- a/tools/sim/HearthCraft_Encounter_Builder.xlsx
+++ b/tools/sim/HearthCraft_Encounter_Builder.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
   <si>
     <t>SIM TUNING SHEET — one row per encounter · columns map 1:1 to simulator controls</t>
   </si>
@@ -837,6 +837,24 @@
   </si>
   <si>
     <t>A cry in the dark, and a deathly cold. It cannot be slain — hold, keep the light, and endure until it withdraws.</t>
+  </si>
+  <si>
+    <t>winCurve</t>
+  </si>
+  <si>
+    <t>simCmd</t>
+  </si>
+  <si>
+    <t>Lv1=25%  Lv2=66%  Lv3=98%  Lv4=100%</t>
+  </si>
+  <si>
+    <t>node run_sim.js --runs 5000 --level 3 --duration 1500 --boss 50000 --drain 12 --spike 75 --spikeiv 13 --rlevel N</t>
+  </si>
+  <si>
+    <t>Lv3=6%  Lv4=81%  Lv6=91%  Lv7=98%  Lv8=100%</t>
+  </si>
+  <si>
+    <t>node run_sim.js --runs 5000 --level 3 --duration 1500 --boss 60000 --drain 18 --spike 75 --spikeiv 9 --rlevel N</t>
   </si>
 </sst>
 </file>
@@ -1406,6 +1424,12 @@
       <c r="Q5" s="18" t="s">
         <v>19</v>
       </c>
+      <c r="R5" t="s">
+        <v>262</v>
+      </c>
+      <c r="S5" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="6" spans="1:17" ns3:dyDescent="0.25">
       <c r="A6" s="19" t="s">
@@ -1459,6 +1483,12 @@
       <c r="Q6" s="19" t="s">
         <v>23</v>
       </c>
+      <c r="R6" t="s">
+        <v>264</v>
+      </c>
+      <c r="S6" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="7" spans="1:17" ns3:dyDescent="0.25">
       <c r="A7" s="19" t="s">
@@ -1511,6 +1541,12 @@
       </c>
       <c r="Q7" s="19" t="s">
         <v>23</v>
+      </c>
+      <c r="R7" t="s">
+        <v>266</v>
+      </c>
+      <c r="S7" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:17" ns3:dyDescent="0.25">
